--- a/docs/数据库字段中英文对照表.xlsx
+++ b/docs/数据库字段中英文对照表.xlsx
@@ -1229,7 +1229,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="22.2666666666667" customWidth="1"/>
@@ -1637,6 +1637,9 @@
         <v>73</v>
       </c>
     </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
